--- a/education_forms/040_school_student_support_audit_form--education_forms.xlsx
+++ b/education_forms/040_school_student_support_audit_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>school_name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>support_level</t>
+          <t>support_level_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Support Level</t>
+          <t>Support Level 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>school_id_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>School Id 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>school_name_choices</t>
+          <t>school_name_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>school_name_choices</t>
+          <t>school_name_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>school_name_choices</t>
+          <t>school_name_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>support_level_choices</t>
+          <t>support_level_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>support_level_choices</t>
+          <t>support_level_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>support_level_choices</t>
+          <t>support_level_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>school_id_choices</t>
+          <t>school_id_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>school_id_choices</t>
+          <t>school_id_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>school_id_choices</t>
+          <t>school_id_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
